--- a/data/trans_orig/IP1008-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108158</t>
+          <t>107970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98248</t>
+          <t>97982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206987</t>
+          <t>206574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71481</t>
+          <t>71329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149542</t>
+          <t>150215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>83570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132286</t>
+          <t>132535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260920</t>
+          <t>260903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,47 +3183,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>8035</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>153311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157948</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163380</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313927</t>
+          <t>314583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320639</t>
+          <t>320648</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,77 +3496,77 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>9021</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>12893</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>12663</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>673350</t>
+          <t>673656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>679837</t>
+          <t>679838</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,82 +3604,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>714502</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>721322</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>713679</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>720682</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1396400</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1390828</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1399729</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>99,72%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1396400</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1391058</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1399961</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101590</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108077</t>
+          <t>107631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211524</t>
+          <t>211512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63619</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69938</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130931</t>
+          <t>131150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137464</t>
+          <t>137448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>51213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110478</t>
+          <t>110404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115551</t>
+          <t>115548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>699019</t>
+          <t>698695</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>705573</t>
+          <t>705570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>740819</t>
+          <t>740983</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>746861</t>
+          <t>746886</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1442876</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451733</t>
+          <t>1451702</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56036</t>
+          <t>56034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113296</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120267</t>
+          <t>120452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72691</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153853</t>
+          <t>153724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159676</t>
+          <t>159531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166258</t>
+          <t>166818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>328019</t>
+          <t>328786</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334307</t>
+          <t>334308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>692806</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>701524</t>
+          <t>701545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>739767</t>
+          <t>739423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744260</t>
+          <t>744257</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1435300</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1444527</t>
+          <t>1445006</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1008-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51831</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48368</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48862</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>169</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107970</t>
+          <t>109330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100901</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97982</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98250</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206574</t>
+          <t>206734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3847</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3757</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74334</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>71329</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>71663</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>228</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150215</t>
+          <t>150125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44138</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41322</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44138</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41308</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134982</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131689</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134982</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>132535</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260903</t>
+          <t>260908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5983</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5479</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162008</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>158075</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>163381</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>156608</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>153311</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>153878</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162008</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>158579</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>314583</t>
+          <t>314567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320648</t>
+          <t>320649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>8886</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8198</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>718599</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>713814</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>721319</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>677801</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>673656</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>679838</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>673241</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>679854</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>718599</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>714502</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>721322</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1390828</t>
+          <t>1390761</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1399729</t>
+          <t>1399822</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4393,102 +4393,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4501,74 +4501,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110552</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108063</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104086</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101558</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>101577</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110552</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107631</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>315</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211512</t>
+          <t>211446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,72 +4731,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1442</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4293</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5357</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4844,74 +4844,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68611</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64635</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69937</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66736</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63885</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63668</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68611</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65227</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69942</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>190</t>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>130457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>137428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1428</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2116</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5873,107 +5873,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54557</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>51213</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>51562</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>114114</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>110627</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>116230</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>114114</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>110404</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>115548</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6794,67 +6794,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7240</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7159</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>744875</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>740902</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>746860</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>703430</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698695</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>705570</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698288</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>705568</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>744875</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>740983</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>746886</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1442893</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451702</t>
+          <t>1451669</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,72 +7368,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3592</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1337</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7521</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7975</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3770</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -7481,72 +7481,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61458</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53779</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49850</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56034</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49396</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>56042</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63826</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>60692</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113616</t>
+          <t>113033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120452</t>
+          <t>120204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,107 +8397,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3829</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4652</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75727</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72617</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73132</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153724</t>
+          <t>153493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9774,67 +9774,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4645</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9882,74 +9882,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>169536</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>166121</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>162767</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>159531</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>159173</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>169536</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>166818</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>512</t>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>328786</t>
+          <t>327967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334308</t>
+          <t>334296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,74 +10112,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11751</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>11767</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742895</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>739136</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744256</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>698136</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>692620</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>701545</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>692604</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>701465</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742895</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>739423</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744257</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1435614</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1445006</t>
+          <t>1445038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
